--- a/auto_tests/ui/simple_ui/data/MangoMock_UI全元素操作测试用例.xlsx
+++ b/auto_tests/ui/simple_ui/data/MangoMock_UI全元素操作测试用例.xlsx
@@ -1520,7 +1520,7 @@
         <x:v>locating, file_path</x:v>
       </x:c>
       <x:c r="K10" s="53" t="str">
-        <x:v>{"file_path":"${project_root}/tests/ui_excel_cases/data/upload.txt"}</x:v>
+        <x:v>{"file_path":"${project_root}/auto_tests/ui/simple_ui/data/upload.txt"}</x:v>
       </x:c>
       <x:c r="L10" s="53" t="str">
         <x:v>打开首页；点击 nav-components；等待 components-page 可见</x:v>
@@ -3792,7 +3792,7 @@
         <x:v>url, timeout</x:v>
       </x:c>
       <x:c r="K50" s="53" t="str">
-        <x:v>{"url":"**/","timeout":5000}</x:v>
+        <x:v>{"url":"**","timeout":5000}</x:v>
       </x:c>
       <x:c r="L50" s="53" t="str">
         <x:v>打开首页；点击 nav-components；等待 components-page 可见</x:v>
@@ -22208,7 +22208,7 @@
         <x:v>w_upload_files</x:v>
       </x:c>
       <x:c r="H101" s="53" t="str">
-        <x:v>{"file_path":"${project_root}/tests/ui_excel_cases/data/upload.txt"}</x:v>
+        <x:v>{"file_path":"${project_root}/auto_tests/ui/simple_ui/data/upload.txt"}</x:v>
       </x:c>
       <x:c r="I101" s="53" t="str">
         <x:v>点击 nav-components</x:v>
@@ -23782,7 +23782,7 @@
         <x:v>传给 w_upload_files</x:v>
       </x:c>
       <x:c r="E15" s="53" t="str">
-        <x:v>${project_root}/tests/ui_excel_cases/data/upload.txt</x:v>
+        <x:v>${project_root}/auto_tests/ui/simple_ui/data/upload.txt</x:v>
       </x:c>
       <x:c r="F15" s="53" t="str">
         <x:v>文件需存在</x:v>
